--- a/output/laminas_comunales/comunal_o_ocup_a_2019_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2019_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,31 +375,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="C2">
-        <v>37.487964630127</v>
+        <v>58.6283302307129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="C3">
-        <v>36.9040565490723</v>
+        <v>51.7860946655273</v>
       </c>
     </row>
     <row r="4">
@@ -414,37 +414,37 @@
         </is>
       </c>
       <c r="C4">
-        <v>31.8586082458496</v>
+        <v>51.3312721252441</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Pozo Almonte</t>
         </is>
       </c>
       <c r="C5">
-        <v>26.6734790802002</v>
+        <v>51.1200714111328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camiña</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C6">
-        <v>17.9086532592773</v>
+        <v>50.3487281799316</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,547 @@
         </is>
       </c>
       <c r="C7">
+        <v>47.4881401062012</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>47.1934394836426</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>46.5676307678223</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>46.403621673584</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>43.999195098877</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>40.5530395507812</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>39.30615234375</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>37.487964630127</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>37.2151908874512</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>36.9040565490723</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>36.5908393859863</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>35.0297813415527</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>33.9822273254395</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>32.8842315673828</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>32.6916580200195</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>31.8586082458496</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>30.7918071746826</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>30.5895862579346</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>30.4694881439209</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>27.5950012207031</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>27.2822360992432</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>26.6734790802002</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>26.4230976104736</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>26.0388317108154</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>22.7360305786133</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>21.6017322540283</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>20.5412368774414</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>19.5219116210938</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>17.9086532592773</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C36">
         <v>16.535814950347</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>14.7837438583374</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>12.2032165527344</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>11.4105796813965</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>11.3686876296997</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>6.33127975463867</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>5.42489814758301</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>2.48962664604187</v>
       </c>
     </row>
   </sheetData>
